--- a/LCA Exports/Fructose_InventoryAssessment.xlsx
+++ b/LCA Exports/Fructose_InventoryAssessment.xlsx
@@ -812,7 +812,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Low Pressure Steam</t>
+          <t>Natural Gas (boiler)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg_ng</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22490.20618518</v>
+        <v>1487.06041683</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9659138123</v>
+        <v>0.4605886941</v>
       </c>
     </row>
     <row r="9">
